--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="338">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T12:03:31+00:00</t>
+    <t>2026-02-04T14:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -514,7 +514,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|ImmunizationRecommendation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -814,10 +814,6 @@
 Reported by</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
-</t>
-  </si>
-  <si>
     <t>Primary result interpreter</t>
   </si>
   <si>
@@ -859,7 +855,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation)
 </t>
   </si>
   <si>
@@ -901,7 +897,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-imagingstudy)
 </t>
   </si>
   <si>
@@ -3758,16 +3754,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O21" t="s" s="2">
         <v>248</v>
@@ -3837,7 +3833,7 @@
         <v>249</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>251</v>
@@ -3848,10 +3844,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3874,19 +3870,19 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -3935,7 +3931,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3953,7 +3949,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>208</v>
@@ -3964,14 +3960,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3990,19 +3986,19 @@
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4039,17 +4035,17 @@
         <v>81</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4067,10 +4063,10 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4078,16 +4074,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="B24" t="s" s="2">
+      <c r="D24" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4106,19 +4102,19 @@
         <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4167,7 +4163,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4185,10 +4181,10 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4196,10 +4192,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4222,16 +4218,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4281,7 +4277,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4302,7 +4298,7 @@
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4310,14 +4306,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4336,17 +4332,17 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -4395,7 +4391,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4413,10 +4409,10 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -4424,10 +4420,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4450,13 +4446,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4507,7 +4503,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4528,7 +4524,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -4536,10 +4532,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4568,7 +4564,7 @@
         <v>137</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>139</v>
@@ -4621,7 +4617,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4642,7 +4638,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -4650,14 +4646,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4679,10 +4675,10 @@
         <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>139</v>
@@ -4737,7 +4733,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4766,10 +4762,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4792,19 +4788,19 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -4853,7 +4849,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4874,7 +4870,7 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -4882,10 +4878,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4908,13 +4904,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4965,7 +4961,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>90</v>
@@ -4986,7 +4982,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -4994,14 +4990,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5020,17 +5016,17 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5079,7 +5075,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5097,10 +5093,10 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5108,10 +5104,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5137,10 +5133,10 @@
         <v>180</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5170,11 +5166,11 @@
         <v>184</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>330</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5191,7 +5187,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5209,10 +5205,10 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5220,10 +5216,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5246,19 +5242,19 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5307,7 +5303,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5325,10 +5321,10 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:21:15+00:00</t>
+    <t>2026-02-04T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:46:20+00:00</t>
+    <t>2026-02-05T06:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T06:51:53+00:00</t>
+    <t>2026-02-05T08:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T08:33:30+00:00</t>
+    <t>2026-02-05T09:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-diagnosticreport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:19:21+00:00</t>
+    <t>2026-02-05T09:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
